--- a/important_mails_2026-05-17.xlsx
+++ b/important_mails_2026-05-17.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H188"/>
+  <dimension ref="A1:H185"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,7 +485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>店铺绩效类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -500,21 +500,69 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Sun, 17 May 2026 08:49:45 +0000</t>
+          <t>Sun, 17 May 2026 14:33:15 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Your payment is on the way</t>
+          <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon Services.
+ We have charged your credit card for $105.47 in an attempt to settle your Amazon seller account balance.
+ Note that the amount charged to your credit card may be less than the total amount you owe due to a credit limit imposed by your bank. If that is the case, we will continue to charge your credit card as often as every 24 hours until the remaining balance in your Amazon seller account is paid in full.
+ You can also use the Make a Payment feature to repay the balance you owe. For more information, see Making a Payment .
+ You can view your payment activity at any time by logging in to your seller account and going to your Payments Report .
+ Thank you for selling on Amazon.
+ Amazon Services
+ Help us improve your experience on selling on Amazon through this brief survey:
+ https://amazonexteu.qualtrics.com/jfe/form/SV_eUKdboEQhg1YpuK?cID=10038096056-202605171349
+ Was this email helpful?
+ SPC-USAmazon-211108450578443</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 17 May 2026 08:49:45 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -534,39 +582,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:47:51 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -586,40 +634,40 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 14:07:57 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>"toys-safety-mv@amazon.com" &lt;toys-safety-mv@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 20326051091] SELLER: A192R36HNXVJ38, ASIN: B0DRTR7GYJ,
  MARKETPLACE: 1 - PS - APPEAL</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Hello,
 We have reviewed your appeal request. We are rejecting your appeal because the detail page has an image of a child playing with the product. We request you take the following action:
@@ -632,39 +680,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 03:03:13 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 You recently received a notice about the removal of your listing(s) for the product(s) listed below.
@@ -684,39 +732,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 08:48:46 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -731,40 +779,40 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Sun, 17 May 2026 05:21:00 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -780,39 +828,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Thu, 14 May 2026 02:39:33 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (ZazNpo+O9J)</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -838,39 +886,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Tue, 12 May 2026 02:56:06 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -883,63 +931,6 @@
 - In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
 - To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
 -</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 10 May 2026 16:45:41 +0000</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (Xq4e6nl040)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-Disposal Summary:
-Quantity Requested: 74
-Quantity Successfully Destroyed: 54
-Quantity Cancelled: 20
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-7548142-6185749
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
---------------------------------------------------------------------------
-Fulfillment by Amazon, professional packing, shipping and servicing of
-online orders.
---------------------------------------------------------------------------
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-USAmazon-2216617652080224</t>
         </is>
       </c>
     </row>
@@ -1875,7 +1866,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1890,75 +1881,21 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Sun, 10 May 2026 16:22:50 +0000</t>
+          <t>Sat, 16 May 2026 04:51:55 +0000</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
+          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Dein Einkaufswagen wartet</t>
+          <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr"/>
       <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
-Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
- 21,81 €
-https://www.amazon.de/gp/product/B0DRCC2H56/?ref_=
-Einkaufswagen anzeigen
-https://www.amazon.de/gp/cart/view.html?ref_=cor
-Schaue dir weitere Optionen an
-SWIMLOOP Premium Schwimmgurt Schwimmtrainer mit 2 x 2 Meter elastischen Gummibändern - Zugseil - Schwimmseil für Pool wie Gegenstromanlage zum Einhängen - Bauchgurt mit Schwimmband Widerstandstraining
- 69,99 €
-https://www.amazon.de/gp/product/B0C7PJVJK3/?ref_=ci_mcx_mr_2p_0_lm
-Schwimmgurt Erwachsene,4m Einstellbare Schwimmgurt Für Pool,Schwimmtrainer Gegenstromanlage Für Pool, Benutzt Für Schwimmingpools Widerstandstraining （Mit Ohrstöpseln und Nasenclip）
- 9,24 €
-https://www.amazon.de/gp/product/B097SKBN2X/?ref_=ci_mcx_mr_2p_1_lm
-BodyCROSS Premium Schwimmtrainer Outdoor – Schwimmgürtel für Kinder &amp;amp; Erwachsene mit Tube (1–20kg), Pool Zubehör, Pull Buoy, Schwimmbrett
- -9 % 114,08 € UVP: 125,97 €
-https://www.amazon.de/gp/product/B01GIMZV8O/?ref_=ci_mcx_mr_2p_2_lm
-TUT Schwimmgürtel, 4-10M S</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 16 May 2026 04:51:55 +0000</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Create FBA removal order by 2026-05-28</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -1982,39 +1919,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:58:34 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-28</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2035,39 +1972,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Sat, 16 May 2026 03:50:26 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -2090,44 +2027,101 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Mon, 11 May 2026 11:38:29 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>You have until July 11 to verify FBA dimensions for fee calculation</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
  96
  As previously communicated, we've updated the way we collect Fulfilment by Amazon (FBA) item package dimensions for products listed in our UK, Germany, France, Italy and Spain stores.
                                                      ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏  ‍͏  ͏ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ ­ ­ ͏‌ ­ ­ </t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 10 May 2026 16:45:41 +0000</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (Xq4e6nl040)</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+Disposal Summary:
+Quantity Requested: 74
+Quantity Successfully Destroyed: 54
+Quantity Cancelled: 20
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral.amazon.com/gp/orders/fba-order-details.html?orderID=S01-7548142-6185749
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+--------------------------------------------------------------------------
+Fulfillment by Amazon, professional packing, shipping and servicing of
+online orders.
+--------------------------------------------------------------------------
+Was this email helpful?
+ https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-USAmazon-2216617652080224</t>
         </is>
       </c>
     </row>
@@ -5057,7 +5051,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -5072,48 +5066,46 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Fri, 17 Apr 2026 11:22:53 +0000</t>
+          <t>Sun, 10 May 2026 16:22:50 +0000</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
+          <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
+          <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr"/>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>尊敬的卖家：
-我们紧急通知您，您在【欧洲】站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】或【已通过】。
-【如何完成合规?】
-您必须与第三方检测、检验和认证服务提供商合作，对收到通知的所有 ASIN 进行商品检测或验证现有的检测文件。请按照以下步骤操作：
-1.前往【绩效】-【账户状况】-【政策合规性】，点击【食品和商品安全问题】。
-2.在【后续步骤】列下，针对需操作的商品点击【提交】-【验证您的商品】。
-3.从清单中选择第三方检测提供商（如需比价，可先查看【从多个提供商获取报价的说明】后再返回选择），点击继续。
-4.确认详细联系信息，点击【确认并继续】。
-5.复制生成的检测申请表编号，提供给所选提供商完成检测
-如果验证现有文件，您必须将由 ISO 17025 认可的实验室出具的检测报告提交至检测、检验和认证服务提供商。
-如何查看TRF状态：在绩效 &gt; 账户状况 &gt; 食品和商品安全问题找到ASIN，点击右方“提交，查看或更新” &gt; “验证您的商品”
-⚠️请注意：
-① 同一ASIN可能只在部分欧洲站点被触发通知，若您计划在欧洲（英国及欧盟）继续销售，只需为每个ASIN任选一个站点完成合规，测试结果将同步至全欧站点。
-② 由于数据可能存在延迟，请务必以卖家平台【绩效 &gt; 账户状况 &gt; 食品和商品安全问题】页面显示的最新状态为准。再次提醒您，为避免下架，请在截止日期之前确保TRF状态更新为【正在验证】或【已通过】。
-③ 如果您认为您的产品不属于【儿童玩具】产品，请选择【申诉请求】选项，提供您认为产品被错误识别的原因进行申诉。
-感谢您的支持，祝您合规大卖！
-如有疑问，请扫码加入亚马逊卖家合规群：
-https://m.media-amazon.com/images/G/01/CN_Compliance_Team/mass_wecom_yt.jpg
-Amazon Global Selling Seller Compliance Team</t>
+          <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
+Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
+ 21,81 €
+https://www.amazon.de/gp/product/B0DRCC2H56/?ref_=
+Einkaufswagen anzeigen
+https://www.amazon.de/gp/cart/view.html?ref_=cor
+Schaue dir weitere Optionen an
+SWIMLOOP Premium Schwimmgurt Schwimmtrainer mit 2 x 2 Meter elastischen Gummibändern - Zugseil - Schwimmseil für Pool wie Gegenstromanlage zum Einhängen - Bauchgurt mit Schwimmband Widerstandstraining
+ 69,99 €
+https://www.amazon.de/gp/product/B0C7PJVJK3/?ref_=ci_mcx_mr_2p_0_lm
+Schwimmgurt Erwachsene,4m Einstellbare Schwimmgurt Für Pool,Schwimmtrainer Gegenstromanlage Für Pool, Benutzt Für Schwimmingpools Widerstandstraining （Mit Ohrstöpseln und Nasenclip）
+ 9,24 €
+https://www.amazon.de/gp/product/B097SKBN2X/?ref_=ci_mcx_mr_2p_1_lm
+BodyCROSS Premium Schwimmtrainer Outdoor – Schwimmgürtel für Kinder &amp;amp; Erwachsene mit Tube (1–20kg), Pool Zubehör, Pull Buoy, Schwimmbrett
+ -9 % 114,08 € UVP: 125,97 €
+https://www.amazon.de/gp/product/B01GIMZV8O/?ref_=ci_mcx_mr_2p_2_lm
+TUT Schwimmgürtel, 4-10M S</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -5128,72 +5120,21 @@
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
-          <t>Thu, 16 Apr 2026 17:53:23 +0000</t>
+          <t>Sat, 9 May 2026 16:23:48 +0000</t>
         </is>
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
+          <t>donotreply@amazon.com</t>
         </is>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>Your Amazon.com Inventory - Action Required</t>
+          <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 4/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 4/2026)</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr"/>
       <c r="H93" s="2" t="inlineStr">
-        <is>
-          <t>Dear Weihai US,
-We have recently restricted listings for the product(s) listed below on Amazon.com.
-Please initiate a removal request for the ASIN(s) referenced below to have your inventory sent to a location of your choosing. If this inventory is not removed within 30 days of this notification (by 05/15/2026), we may dispose of it in accordance with FBA policies.
-Thank you for your attention to this matter.
-Regards,
-Product Safety Team
-Amazon.com
-www.amazon.com
-Please note: this e-mail was sent from a notification-only address that cannot accept incoming e-mail. Please do not reply to this message.
-Affected Product(s):
-B0FCDRNTT8
-Was this email helpful?
- https://sellercentral.amazon.com/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=RESTRICTED_LISTING_PRODUCTS_REMOVAL_REQUEST
-SPC-USAmazon-1864773927693727</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 9 May 2026 16:23:48 +0000</t>
-        </is>
-      </c>
-      <c r="E94" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F94" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 4/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 4/2026)</t>
-        </is>
-      </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -5212,39 +5153,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 08:34:05 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5256,39 +5197,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:22:14 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5300,39 +5241,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 07:02:56 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 4/2026</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 4/2026 is now available in your Seller Central Account.
@@ -5344,39 +5285,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:29:17 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5388,39 +5329,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:25:39 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5432,39 +5373,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:10:57 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5476,39 +5417,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:09:44 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -5527,39 +5468,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 22:01:18 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 4/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -5578,39 +5519,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:25:07 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 4 2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 4 i rok 2026.
@@ -5622,39 +5563,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:24:35 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -5666,39 +5607,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 21:03:04 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -5710,39 +5651,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 20:51:50 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5754,39 +5695,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:44:14 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 4 2026</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 4 i rok 2026.
@@ -5798,39 +5739,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:35:59 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -5842,39 +5783,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:24:07 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5886,39 +5827,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 18:18:06 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5930,39 +5871,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:33:15 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -5974,39 +5915,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 16:20:52 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6018,39 +5959,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:43:38 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 4/2026</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -6062,39 +6003,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 15:17:48 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6106,39 +6047,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:52:53 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6150,40 +6091,40 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 14:40:42 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 4/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 4/2026)</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 4 2026 nu beschikbaar is in je Seller Central-account.
@@ -6202,39 +6143,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:57:28 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6246,39 +6187,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:43:13 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 4/2026</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 4/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6290,39 +6231,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 13:40:52 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6334,39 +6275,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:55:06 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 4.2026</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 4.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6378,39 +6319,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:49:29 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 4/2026</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6422,39 +6363,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 8 May 2026 11:20:15 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -6475,39 +6416,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 15:00:42 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -6522,39 +6463,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Wed, 6 May 2026 14:24:59 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ae Merchant Invoice for 4/2026 (Amazon.ae فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 4/2026)</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 4/2026 is now available in your Seller Central Account.
@@ -6573,39 +6514,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Sun, 3 May 2026 05:32:15 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -6627,39 +6568,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 15:27:47 +0600</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Deals &lt;amazonreviewsdeals1@gmail.com&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Amazon Review Rating Deals</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>Not getting sales on Amazon? Even after doing everything right? Then this
 message is for you!
@@ -6685,40 +6626,40 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 03:15:52 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -6734,40 +6675,40 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:51 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -6783,39 +6724,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 02:15:45 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -6831,39 +6772,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 01:23:15 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -6879,39 +6820,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 15:09:15 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -6927,39 +6868,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 14:16:19 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -6973,39 +6914,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:33:13 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 04/2026</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -7023,40 +6964,40 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:34 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -7072,39 +7013,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 02:13:30 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -7120,39 +7061,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:21:43 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -7168,40 +7109,40 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 01:18:50 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -7217,39 +7158,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:55:17 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -7266,39 +7207,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 21:32:46 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Prime Day 业绩
 尊敬的卖家，
@@ -7327,39 +7268,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 15:08:42 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -7375,39 +7316,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:12:49 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -7421,39 +7362,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 14:07:32 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -7468,39 +7409,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Thu, 30 Apr 2026 10:18:53 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -7520,39 +7461,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 20:59:56 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para mayo</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para mayo
@@ -7581,40 +7522,40 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:37:52 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Il team di Gestione multicanale &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Aggiornamenti ai costi di Gestione multicanale in vigore dal 29
  maggio 2026</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
  Stiamo aggiornando le tariffe di Gestione multicanale per aiutarti a ridurre i costi e investire nella crescita della tua attività.
@@ -7627,39 +7568,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:30:37 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>The Multichannel Fulfillment team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>MCF fee updates effective May 29, 2026</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  We’re updating our Multichannel Fulfillment fees to help you reduce your costs so you can invest in growing your business.
@@ -7674,39 +7615,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Wed, 29 Apr 2026 14:25:56 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>El Departamento de Logística Multicanal &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Actualización de las tarifas de Logística Multicanal en vigor a partir del 29 de mayo de 2026</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
  Vamos a actualizar nuestras tarifas de Logística Multicanal para ayudarte a reducir los costes y así puedas invertir en hacer crecer tu negocio.
@@ -7719,40 +7660,40 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:38:42 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Presenta documentos de cumplimiento normativo del producto para
  evitar que se retiren los listings</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta documentos de cumplimiento normativo del producto para evitar que se retiren los listings
@@ -7767,40 +7708,40 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:25:34 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Documenten over productconformiteit indienen om verwijdering van
  productvermeldingen te voorkomen</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
  Documenten over productconformiteit indienen om verwijdering van productvermeldingen te voorkomen
@@ -7814,39 +7755,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 17:06:50 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Prześlij dokumenty zgodności dotyczące produktu, aby zapobiec usunięciu oferty
@@ -7860,39 +7801,39 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:58:32 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in dokument om produktöverensstämmelse för att undvika att produktposter tas bort
@@ -7907,39 +7848,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:54:06 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione di conformità dei prodotti per evitare la rimozione delle offerte
@@ -7953,39 +7894,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 16:50:08 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettez les documents de conformité des produits pour éviter le retrait de la mise en vente
@@ -8000,39 +7941,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 15:58:40 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -8047,39 +7988,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Mon, 27 Apr 2026 05:22:10 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 100 × 150cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Gril Matte
@@ -8098,39 +8039,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Sun, 26 Apr 2026 11:10:42 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -8146,39 +8087,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 05:38:32 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -8199,39 +8140,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:19:11 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -8249,40 +8190,40 @@
         </is>
       </c>
     </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:18:24 +0000</t>
         </is>
       </c>
-      <c r="E159" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F159" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -8300,39 +8241,39 @@
         </is>
       </c>
     </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:15:32 +0000</t>
         </is>
       </c>
-      <c r="E160" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F160" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -8349,39 +8290,39 @@
         </is>
       </c>
     </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:50 +0000</t>
         </is>
       </c>
-      <c r="E161" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F161" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G161" s="2" t="inlineStr"/>
-      <c r="H161" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -8399,40 +8340,40 @@
         </is>
       </c>
     </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:12:30 +0000</t>
         </is>
       </c>
-      <c r="E162" s="2" t="inlineStr">
+      <c r="E161" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F162" s="2" t="inlineStr">
+      <c r="F161" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G162" s="2" t="inlineStr"/>
-      <c r="H162" s="2" t="inlineStr">
+      <c r="G161" s="2" t="inlineStr"/>
+      <c r="H161" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -8450,39 +8391,39 @@
         </is>
       </c>
     </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 19:09:22 +0000</t>
         </is>
       </c>
-      <c r="E163" s="2" t="inlineStr">
+      <c r="E162" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F163" s="2" t="inlineStr">
+      <c r="F162" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G163" s="2" t="inlineStr"/>
-      <c r="H163" s="2" t="inlineStr">
+      <c r="G162" s="2" t="inlineStr"/>
+      <c r="H162" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -8500,39 +8441,39 @@
         </is>
       </c>
     </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="inlineStr">
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="inlineStr">
         <is>
           <t>Thu, 23 Apr 2026 00:31:36 +0000</t>
         </is>
       </c>
-      <c r="E164" s="2" t="inlineStr">
+      <c r="E163" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F164" s="2" t="inlineStr">
+      <c r="F163" s="2" t="inlineStr">
         <is>
           <t>规划您的 La French Week 促销活动</t>
         </is>
       </c>
-      <c r="G164" s="2" t="inlineStr"/>
-      <c r="H164" s="2" t="inlineStr">
+      <c r="G163" s="2" t="inlineStr"/>
+      <c r="H163" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -8549,39 +8490,39 @@
         </is>
       </c>
     </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E165" s="2" t="inlineStr">
+      <c r="E164" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F165" s="2" t="inlineStr">
+      <c r="F164" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G165" s="2" t="inlineStr"/>
-      <c r="H165" s="2" t="inlineStr">
+      <c r="G164" s="2" t="inlineStr"/>
+      <c r="H164" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8596,39 +8537,39 @@
         </is>
       </c>
     </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="inlineStr">
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="inlineStr">
         <is>
           <t>Wed, 22 Apr 2026 07:42:42 +0000</t>
         </is>
       </c>
-      <c r="E166" s="2" t="inlineStr">
+      <c r="E165" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F166" s="2" t="inlineStr">
+      <c r="F165" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G166" s="2" t="inlineStr"/>
-      <c r="H166" s="2" t="inlineStr">
+      <c r="G165" s="2" t="inlineStr"/>
+      <c r="H165" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -8647,39 +8588,39 @@
         </is>
       </c>
     </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="inlineStr">
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:32:20 +0000</t>
         </is>
       </c>
-      <c r="E167" s="2" t="inlineStr">
+      <c r="E166" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F167" s="2" t="inlineStr">
+      <c r="F166" s="2" t="inlineStr">
         <is>
           <t>Prime Day：立即提报您的促销</t>
         </is>
       </c>
-      <c r="G167" s="2" t="inlineStr"/>
-      <c r="H167" s="2" t="inlineStr">
+      <c r="G166" s="2" t="inlineStr"/>
+      <c r="H166" s="2" t="inlineStr">
         <is>
           <t>Prime Day（日期待公布）：立即提报您的促销
 尊敬的卖家，
@@ -8697,39 +8638,39 @@
         </is>
       </c>
     </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="inlineStr">
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:19:47 +0000</t>
         </is>
       </c>
-      <c r="E168" s="2" t="inlineStr">
+      <c r="E167" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F168" s="2" t="inlineStr">
+      <c r="F167" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以重新启售商品</t>
         </is>
       </c>
-      <c r="G168" s="2" t="inlineStr"/>
-      <c r="H168" s="2" t="inlineStr">
+      <c r="G167" s="2" t="inlineStr"/>
+      <c r="H167" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品安全文件以重新启售商品
@@ -8768,39 +8709,39 @@
         </is>
       </c>
     </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:42 +0000</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="E168" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
+      <c r="F168" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G169" s="2" t="inlineStr"/>
-      <c r="H169" s="2" t="inlineStr">
+      <c r="G168" s="2" t="inlineStr"/>
+      <c r="H168" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -8816,40 +8757,40 @@
         </is>
       </c>
     </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="inlineStr">
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:17:14 +0000</t>
         </is>
       </c>
-      <c r="E170" s="2" t="inlineStr">
+      <c r="E169" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F170" s="2" t="inlineStr">
+      <c r="F169" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G170" s="2" t="inlineStr"/>
-      <c r="H170" s="2" t="inlineStr">
+      <c r="G169" s="2" t="inlineStr"/>
+      <c r="H169" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -8865,39 +8806,39 @@
         </is>
       </c>
     </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:36 +0000</t>
         </is>
       </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="E170" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
+      <c r="F170" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G171" s="2" t="inlineStr"/>
-      <c r="H171" s="2" t="inlineStr">
+      <c r="G170" s="2" t="inlineStr"/>
+      <c r="H170" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -8913,39 +8854,39 @@
         </is>
       </c>
     </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="inlineStr">
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:13:34 +0000</t>
         </is>
       </c>
-      <c r="E172" s="2" t="inlineStr">
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F172" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G172" s="2" t="inlineStr"/>
-      <c r="H172" s="2" t="inlineStr">
+      <c r="G171" s="2" t="inlineStr"/>
+      <c r="H171" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -8959,40 +8900,40 @@
         </is>
       </c>
     </row>
-    <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:11:30 +0000</t>
         </is>
       </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="E172" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
+      <c r="F172" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr"/>
-      <c r="H173" s="2" t="inlineStr">
+      <c r="G172" s="2" t="inlineStr"/>
+      <c r="H172" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -9008,39 +8949,39 @@
         </is>
       </c>
     </row>
-    <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B174" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C174" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D174" s="2" t="inlineStr">
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
         <is>
           <t>Tue, 21 Apr 2026 09:09:39 +0000</t>
         </is>
       </c>
-      <c r="E174" s="2" t="inlineStr">
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F174" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G174" s="2" t="inlineStr"/>
-      <c r="H174" s="2" t="inlineStr">
+      <c r="G173" s="2" t="inlineStr"/>
+      <c r="H173" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -9056,39 +8997,39 @@
         </is>
       </c>
     </row>
-    <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
         <is>
           <t>Mon, 20 Apr 2026 05:22:42 +0000</t>
         </is>
       </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="E174" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
+      <c r="F174" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr"/>
-      <c r="H175" s="2" t="inlineStr">
+      <c r="G174" s="2" t="inlineStr"/>
+      <c r="H174" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -9109,39 +9050,39 @@
         </is>
       </c>
     </row>
-    <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B176" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C176" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D176" s="2" t="inlineStr">
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 15:14:51 +0000</t>
         </is>
       </c>
-      <c r="E176" s="2" t="inlineStr">
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F176" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr"/>
-      <c r="H176" s="2" t="inlineStr">
+      <c r="G175" s="2" t="inlineStr"/>
+      <c r="H175" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -9156,88 +9097,39 @@
         </is>
       </c>
     </row>
-    <row r="177">
-      <c r="A177" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B177" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C177" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D177" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 17 Apr 2026 09:39:52 +0000</t>
-        </is>
-      </c>
-      <c r="E177" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F177" s="2" t="inlineStr">
-        <is>
-          <t>Verify your primary operating address for tax purposes</t>
-        </is>
-      </c>
-      <c r="G177" s="2" t="inlineStr"/>
-      <c r="H177" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Amazon Services
- Verify your primary operating address for tax purposes
- Hello,
-To ensure the pertinent tax treatment is applied to your account, you must confirm your primary operating address . To help you, we’ve introduced a new field in Seller Central, called primary operating address.
-This allows us to determine your establishment for tax purposes. If your information isn’t listed correctly, your taxes will also be incorrect.
- Your primary operating address or primary place of business is the physical location where you conduct your main day-to-day business activities. This can be either:
-- Where your central administration functions take place.
-- Where you have sufficient degree of permanence and an established presence in terms of human resources, technical resources, and infrastructure to run your business operations (e.g., where your employees are located).
- Here's how to verify your primary operating address:
-- Go to your Identity Information page .
-- If the pre-filled information is correct, click I confirm that my primary operating address is correct .
-- If it's incorrect, click Edit information and provide a valid primary operating address by selecting a saved address </t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B178" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C178" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 04:43:42 +0000</t>
         </is>
       </c>
-      <c r="E178" s="2" t="inlineStr">
+      <c r="E176" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F178" s="2" t="inlineStr">
+      <c r="F176" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-21</t>
         </is>
       </c>
-      <c r="G178" s="2" t="inlineStr"/>
-      <c r="H178" s="2" t="inlineStr">
+      <c r="G176" s="2" t="inlineStr"/>
+      <c r="H176" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9261,39 +9153,39 @@
         </is>
       </c>
     </row>
-    <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B179" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C179" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
         <is>
           <t>Sat, 9 May 2026 03:34:49 +0000</t>
         </is>
       </c>
-      <c r="E179" s="2" t="inlineStr">
+      <c r="E177" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F179" s="2" t="inlineStr">
+      <c r="F177" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G179" s="2" t="inlineStr"/>
-      <c r="H179" s="2" t="inlineStr">
+      <c r="G177" s="2" t="inlineStr"/>
+      <c r="H177" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9316,39 +9208,39 @@
         </is>
       </c>
     </row>
-    <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B180" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C180" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D180" s="2" t="inlineStr">
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
         <is>
           <t>Sat, 2 May 2026 04:46:00 +0000</t>
         </is>
       </c>
-      <c r="E180" s="2" t="inlineStr">
+      <c r="E178" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F180" s="2" t="inlineStr">
+      <c r="F178" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G180" s="2" t="inlineStr"/>
-      <c r="H180" s="2" t="inlineStr">
+      <c r="G178" s="2" t="inlineStr"/>
+      <c r="H178" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9372,39 +9264,39 @@
         </is>
       </c>
     </row>
-    <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B181" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C181" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D181" s="2" t="inlineStr">
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 04:25:43 +0000</t>
         </is>
       </c>
-      <c r="E181" s="2" t="inlineStr">
+      <c r="E179" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F181" s="2" t="inlineStr">
+      <c r="F179" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr"/>
-      <c r="H181" s="2" t="inlineStr">
+      <c r="G179" s="2" t="inlineStr"/>
+      <c r="H179" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9428,39 +9320,39 @@
         </is>
       </c>
     </row>
-    <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B182" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C182" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D182" s="2" t="inlineStr">
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
         <is>
           <t>Sat, 25 Apr 2026 03:35:07 +0000</t>
         </is>
       </c>
-      <c r="E182" s="2" t="inlineStr">
+      <c r="E180" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F182" s="2" t="inlineStr">
+      <c r="F180" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-05-07</t>
         </is>
       </c>
-      <c r="G182" s="2" t="inlineStr"/>
-      <c r="H182" s="2" t="inlineStr">
+      <c r="G180" s="2" t="inlineStr"/>
+      <c r="H180" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9481,39 +9373,39 @@
         </is>
       </c>
     </row>
-    <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B183" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C183" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 04:00:50 +0000</t>
         </is>
       </c>
-      <c r="E183" s="2" t="inlineStr">
+      <c r="E181" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F183" s="2" t="inlineStr">
+      <c r="F181" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-30</t>
         </is>
       </c>
-      <c r="G183" s="2" t="inlineStr"/>
-      <c r="H183" s="2" t="inlineStr">
+      <c r="G181" s="2" t="inlineStr"/>
+      <c r="H181" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -9535,39 +9427,39 @@
         </is>
       </c>
     </row>
-    <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B184" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C184" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D184" s="2" t="inlineStr">
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 03:30:46 +0000</t>
         </is>
       </c>
-      <c r="E184" s="2" t="inlineStr">
+      <c r="E182" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F184" s="2" t="inlineStr">
+      <c r="F182" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G184" s="2" t="inlineStr"/>
-      <c r="H184" s="2" t="inlineStr">
+      <c r="G182" s="2" t="inlineStr"/>
+      <c r="H182" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -9590,39 +9482,39 @@
         </is>
       </c>
     </row>
-    <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B185" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C185" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D185" s="2" t="inlineStr">
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
         <is>
           <t>Fri, 1 May 2026 00:16:37 +0000</t>
         </is>
       </c>
-      <c r="E185" s="2" t="inlineStr">
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F185" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G185" s="2" t="inlineStr"/>
-      <c r="H185" s="2" t="inlineStr">
+      <c r="G183" s="2" t="inlineStr"/>
+      <c r="H183" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -9652,39 +9544,39 @@
         </is>
       </c>
     </row>
-    <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+    <row r="184">
+      <c r="A184" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B186" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C186" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D186" s="2" t="inlineStr">
+      <c r="B184" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C184" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D184" s="2" t="inlineStr">
         <is>
           <t>Tue, 28 Apr 2026 18:05:15 +0000</t>
         </is>
       </c>
-      <c r="E186" s="2" t="inlineStr">
+      <c r="E184" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F186" s="2" t="inlineStr">
+      <c r="F184" s="2" t="inlineStr">
         <is>
           <t>提交商品合规文件，以避免商品被移除</t>
         </is>
       </c>
-      <c r="G186" s="2" t="inlineStr"/>
-      <c r="H186" s="2" t="inlineStr">
+      <c r="G184" s="2" t="inlineStr"/>
+      <c r="H184" s="2" t="inlineStr">
         <is>
           <t>96
  提交商品合规文件，以避免商品被移除
@@ -9733,39 +9625,39 @@
         </is>
       </c>
     </row>
-    <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+    <row r="185">
+      <c r="A185" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B187" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C187" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D187" s="2" t="inlineStr">
+      <c r="B185" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C185" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D185" s="2" t="inlineStr">
         <is>
           <t>Sat, 18 Apr 2026 11:41:39 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E187" s="2" t="inlineStr">
+      <c r="E185" s="2" t="inlineStr">
         <is>
           <t>GTTC国际业务部玩具组 &lt;gttctoy@cngttc.cn&gt;</t>
         </is>
       </c>
-      <c r="F187" s="2" t="inlineStr">
+      <c r="F185" s="2" t="inlineStr">
         <is>
           <t>AMAZON DV TIC TRF ID--Top urgently</t>
         </is>
       </c>
-      <c r="G187" s="2" t="inlineStr"/>
-      <c r="H187" s="2" t="inlineStr">
+      <c r="G185" s="2" t="inlineStr"/>
+      <c r="H185" s="2" t="inlineStr">
         <is>
           <t>Dear Vendor,        Some of your TR numbers on Amazon have been pending in our backend for a long time without timely processing. We plan to automatically clear all unresponded TR numbers in our system two days later.
 If you have any TR numbers that require sample submission for testing, please reply to this email and send us the corresponding TR numbers within two days, and contact our relevant customer service within one week to arrange sample submission.
@@ -9774,54 +9666,6 @@
         </is>
       </c>
     </row>
-    <row r="188">
-      <c r="A188" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B188" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C188" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D188" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 17 Apr 2026 02:18:44 +0000</t>
-        </is>
-      </c>
-      <c r="E188" s="2" t="inlineStr">
-        <is>
-          <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F188" s="2" t="inlineStr">
-        <is>
-          <t>[Action Required] – Update Inventory -FBA</t>
-        </is>
-      </c>
-      <c r="G188" s="2" t="inlineStr"/>
-      <c r="H188" s="2" t="inlineStr">
-        <is>
-          <t>Dear Seller,
-This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
-We recommend that you inbound additional inventory for your products immediately. To view the recommended replenishment quantity for these ASINs, go to “Restock inventory”:
-https://sellercentral.amazon.ca/restockinventory/recommendations
-Here is a sample of your high selling FBA ASINs, which are considered low in stock at the moment:
-B0DMFL5X12
-You can download the full list of your ASIN at risk of out of stock at the following link:  https://www.sellercentral.amazon.ca/reportcentral/RestockReport/1
-For more information about Restock tool, you can visit this help page - https://sellercentral.amazon.ca/gp/help/G201634550
-If you need further help, please raise a case via contact us. - https://sellercentral.amazon.ca/cu/contact-us?ref=xx_ContactUs_xxxx_helphub
-If you are not the correct point of contact, please re-direct this report to the correct point of contact.
-If you wish to unsubscribe please REPLY ALL with the subject line ‘Unsubsc</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
